--- a/panchang-data/Somnath2026.xlsx
+++ b/panchang-data/Somnath2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5396">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16213,6 +16213,9 @@
   </si>
   <si>
     <t>121°05'01.58</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16702,7 +16705,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16788,7 +16791,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16874,7 +16877,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16960,7 +16963,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17046,7 +17049,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17132,7 +17135,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17218,7 +17221,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17304,7 +17307,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17390,7 +17393,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17476,7 +17479,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17562,7 +17565,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17648,7 +17651,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17734,7 +17737,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17820,7 +17823,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17906,7 +17909,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17992,7 +17995,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18078,7 +18081,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18164,7 +18167,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18250,7 +18253,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18336,7 +18339,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18422,7 +18425,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18508,7 +18511,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18594,7 +18597,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18680,7 +18683,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18766,7 +18769,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18852,7 +18855,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18938,7 +18941,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19024,7 +19027,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19110,7 +19113,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19196,7 +19199,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19282,7 +19285,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19368,7 +19371,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19454,7 +19457,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19540,7 +19543,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19626,7 +19629,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19712,7 +19715,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19798,7 +19801,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19884,7 +19887,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19970,7 +19973,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20056,7 +20059,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20142,7 +20145,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20228,7 +20231,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20314,7 +20317,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20400,7 +20403,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20486,7 +20489,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20572,7 +20575,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20658,7 +20661,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20744,7 +20747,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20830,7 +20833,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20916,7 +20919,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21002,7 +21005,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21088,7 +21091,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21174,7 +21177,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21260,7 +21263,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21346,7 +21349,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21432,7 +21435,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21518,7 +21521,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21604,7 +21607,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21690,7 +21693,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21776,7 +21779,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21862,7 +21865,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21948,7 +21951,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22034,7 +22037,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22120,7 +22123,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22206,7 +22209,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22292,7 +22295,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22378,7 +22381,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22464,7 +22467,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22550,7 +22553,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22636,7 +22639,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22722,7 +22725,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22808,7 +22811,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22894,7 +22897,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22980,7 +22983,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23066,7 +23069,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23152,7 +23155,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23238,7 +23241,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23324,7 +23327,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23410,7 +23413,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23496,7 +23499,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23582,7 +23585,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23668,7 +23671,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23754,7 +23757,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23840,7 +23843,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23926,7 +23929,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24012,7 +24015,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24098,7 +24101,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24184,7 +24187,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24270,7 +24273,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24356,7 +24359,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24442,7 +24445,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24528,7 +24531,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1009</v>
+        <v>1452</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24614,7 +24617,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24700,7 +24703,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24786,7 +24789,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24872,7 +24875,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24958,7 +24961,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25044,7 +25047,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25130,7 +25133,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25216,7 +25219,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25302,7 +25305,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25388,7 +25391,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25474,7 +25477,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25560,7 +25563,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25646,7 +25649,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25732,7 +25735,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25818,7 +25821,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25904,7 +25907,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25990,7 +25993,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26076,7 +26079,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26162,7 +26165,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26248,7 +26251,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26334,7 +26337,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26420,7 +26423,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26506,7 +26509,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26592,7 +26595,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26678,7 +26681,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26764,7 +26767,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26850,7 +26853,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26936,7 +26939,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27022,7 +27025,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1452</v>
+        <v>1877</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27108,7 +27111,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27194,7 +27197,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27280,7 +27283,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27366,7 +27369,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27452,7 +27455,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27538,7 +27541,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27624,7 +27627,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27710,7 +27713,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27796,7 +27799,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27882,7 +27885,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27968,7 +27971,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28054,7 +28057,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28140,7 +28143,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28226,7 +28229,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28312,7 +28315,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1877</v>
+        <v>2313</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28398,7 +28401,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28484,7 +28487,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28570,7 +28573,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28656,7 +28659,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28742,7 +28745,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28828,7 +28831,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28914,7 +28917,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29000,7 +29003,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29086,7 +29089,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29172,7 +29175,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29258,7 +29261,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29344,7 +29347,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29430,7 +29433,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29516,7 +29519,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29602,7 +29605,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1877</v>
+        <v>5395</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29688,7 +29691,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29774,7 +29777,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29860,7 +29863,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29946,7 +29949,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30032,7 +30035,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30118,7 +30121,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30204,7 +30207,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30290,7 +30293,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30376,7 +30379,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30462,7 +30465,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30548,7 +30551,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30634,7 +30637,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30720,7 +30723,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30806,7 +30809,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30892,7 +30895,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2313</v>
+        <v>5395</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
